--- a/tableau_synthese.xlsx
+++ b/tableau_synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eliott\Desktop\Portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71F43CB-400D-4FBF-8E01-B5C1F78B173B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365ADA28-B4A6-4901-A66B-4B7FA7322317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -131,6 +131,15 @@
   </si>
   <si>
     <t xml:space="preserve">X </t>
+  </si>
+  <si>
+    <t>Intsallation Linux</t>
+  </si>
+  <si>
+    <t>Installation + Condifuration De GLPI</t>
+  </si>
+  <si>
+    <t>Traitement des tickets</t>
   </si>
 </sst>
 </file>
@@ -586,6 +595,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -594,27 +624,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -895,56 +904,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="30"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32" t="s">
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
       <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
@@ -955,22 +964,22 @@
       <c r="K4" s="29"/>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
     </row>
     <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="35" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -993,8 +1002,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="9" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="36"/>
-      <c r="B7" s="37"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="7" t="s">
         <v>13</v>
       </c>
@@ -1015,20 +1024,22 @@
       </c>
     </row>
     <row r="8" spans="1:13" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
     </row>
     <row r="9" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="10"/>
-      <c r="B9" s="39">
+      <c r="A9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="30">
         <v>45952</v>
       </c>
       <c r="C9" s="26"/>
@@ -1045,8 +1056,10 @@
       <c r="H9" s="13"/>
     </row>
     <row r="10" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10"/>
-      <c r="B10" s="39">
+      <c r="A10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="30">
         <v>46344</v>
       </c>
       <c r="C10" s="27"/>
@@ -1074,39 +1087,23 @@
     </row>
     <row r="12" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10"/>
-      <c r="B12" s="39">
-        <v>46372</v>
-      </c>
+      <c r="B12" s="30"/>
       <c r="C12" s="26"/>
-      <c r="D12" s="24" t="s">
-        <v>26</v>
-      </c>
+      <c r="D12" s="24"/>
       <c r="E12" s="24"/>
-      <c r="F12" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>27</v>
-      </c>
+      <c r="F12" s="24"/>
+      <c r="G12" s="27"/>
       <c r="H12" s="13"/>
     </row>
     <row r="13" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10"/>
-      <c r="B13" s="39">
-        <v>46070</v>
-      </c>
+      <c r="B13" s="30"/>
       <c r="C13" s="27"/>
-      <c r="D13" s="24" t="s">
-        <v>26</v>
-      </c>
+      <c r="D13" s="24"/>
       <c r="E13" s="24"/>
       <c r="F13" s="24"/>
-      <c r="G13" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>26</v>
-      </c>
+      <c r="G13" s="27"/>
+      <c r="H13" s="13"/>
     </row>
     <row r="14" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10"/>
@@ -1219,26 +1216,36 @@
       <c r="H24" s="13"/>
     </row>
     <row r="25" spans="1:8" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="33"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
     </row>
     <row r="26" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="10"/>
-      <c r="B26" s="11"/>
+      <c r="A26" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="30">
+        <v>46070</v>
+      </c>
       <c r="C26" s="24"/>
       <c r="D26" s="27"/>
       <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="25"/>
+      <c r="F26" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="25" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="27" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10"/>
@@ -1301,16 +1308,16 @@
       <c r="H32" s="25"/>
     </row>
     <row r="33" spans="1:8" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="33" t="s">
+      <c r="A33" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
     </row>
     <row r="34" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="10"/>
@@ -1394,6 +1401,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A33:H33"/>
     <mergeCell ref="A4:E4"/>
@@ -1401,11 +1413,6 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.196527777777778" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
